--- a/output/pdf_financials_xlsx/MAZ.H.xlsx
+++ b/output/pdf_financials_xlsx/MAZ.H.xlsx
@@ -7950,10 +7950,10 @@
         </is>
       </c>
       <c r="E142" s="5" t="n">
-        <v>2.412</v>
+        <v>-2.412</v>
       </c>
       <c r="F142" s="5" t="n">
-        <v>0.528</v>
+        <v>-0.528</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/MAZ.H.xlsx
+++ b/output/pdf_financials_xlsx/MAZ.H.xlsx
@@ -1085,16 +1085,16 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1.458</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1.373</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.909</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>1.519</v>
       </c>
     </row>
     <row r="35">
@@ -1123,16 +1123,16 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>1.458</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>1.373</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.909</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>1.519</v>
       </c>
     </row>
     <row r="37">
@@ -1351,16 +1351,16 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>6.702</v>
+        <v>5.244</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>5.382</v>
+        <v>4.009</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>5.026</v>
+        <v>4.117</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>12.243</v>
+        <v>10.724</v>
       </c>
     </row>
     <row r="49">
@@ -3128,7 +3128,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">

--- a/output/pdf_financials_xlsx/MAZ.H.xlsx
+++ b/output/pdf_financials_xlsx/MAZ.H.xlsx
@@ -983,16 +983,16 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0</v>
+        <v>0.048</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0</v>
+        <v>0.094</v>
       </c>
     </row>
     <row r="29">
@@ -1002,16 +1002,16 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.53</v>
+        <v>-0.51</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>2.817</v>
+        <v>2.865</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>2.328</v>
+        <v>2.412</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-26.039</v>
+        <v>-25.945</v>
       </c>
     </row>
     <row r="30">
@@ -1021,16 +1021,16 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-36.17747440273038</v>
+        <v>-34.8122866894198</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>53.9965497412306</v>
+        <v>54.91661874640597</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>23.63451776649746</v>
+        <v>24.48730964467005</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-449.8013473829677</v>
+        <v>-448.1775781654862</v>
       </c>
     </row>
     <row r="31">
@@ -2343,16 +2343,16 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>0.048</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>0.094</v>
       </c>
     </row>
     <row r="101">
@@ -4610,7 +4610,11 @@
           <t>Depreciation of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E45" s="5" t="n">
         <v>0.02</v>
       </c>

--- a/output/pdf_financials_xlsx/MAZ.H.xlsx
+++ b/output/pdf_financials_xlsx/MAZ.H.xlsx
@@ -1511,16 +1511,16 @@
         </is>
       </c>
       <c r="B56" s="3" t="n">
-        <v>0</v>
+        <v>1.282</v>
       </c>
       <c r="C56" s="3" t="n">
-        <v>0</v>
+        <v>1.426</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>0</v>
+        <v>1.478</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>0</v>
+        <v>1.585</v>
       </c>
     </row>
     <row r="57">
@@ -1530,16 +1530,16 @@
         </is>
       </c>
       <c r="B57" s="3" t="n">
-        <v>0</v>
+        <v>0.117</v>
       </c>
       <c r="C57" s="3" t="n">
-        <v>0</v>
+        <v>0.165</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>0</v>
+        <v>0.249</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>0</v>
+        <v>0.342</v>
       </c>
     </row>
     <row r="58">
@@ -2915,15 +2915,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D129" s="3" t="n">
+        <v>0.122</v>
+      </c>
+      <c r="E129" s="3" t="n">
+        <v>27.889</v>
       </c>
     </row>
     <row r="130">
@@ -3027,25 +3023,17 @@
           <t>Free Cash Flow</t>
         </is>
       </c>
-      <c r="B135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B135" s="3" t="n">
+        <v>-0.669</v>
+      </c>
+      <c r="C135" s="3" t="n">
+        <v>1.807</v>
+      </c>
+      <c r="D135" s="3" t="n">
+        <v>-0.065</v>
+      </c>
+      <c r="E135" s="3" t="n">
+        <v>-21.652</v>
       </c>
     </row>
   </sheetData>
@@ -5032,7 +5020,11 @@
           <t>Net cash generated by (used in) operating activities</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E58" s="5" t="n">
         <v>-0.623</v>
       </c>
